--- a/data/trans_bre/DCD-Clase-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,38</t>
+          <t>2,54; 11,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,14</t>
+          <t>-1,5; 5,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 15,17</t>
+          <t>7,21; 15,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,64; 339,18</t>
+          <t>41,47; 347,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 144,34</t>
+          <t>-22,47; 144,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,1; 219,47</t>
+          <t>63,82; 207,4</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,61</t>
+          <t>3,22; 12,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,24</t>
+          <t>2,11; 10,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 16,26</t>
+          <t>7,74; 17,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,57; 341,03</t>
+          <t>42,3; 332,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,37; 316,81</t>
+          <t>30,87; 355,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,02; 193,59</t>
+          <t>62,59; 212,27</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 10,12</t>
+          <t>-0,07; 9,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 19,29</t>
+          <t>5,82; 18,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,78; 33,96</t>
+          <t>16,13; 32,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 142,84</t>
+          <t>-2,52; 136,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,08; 362,73</t>
+          <t>73,99; 336,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>103,54; 901,71</t>
+          <t>108,68; 844,01</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,31</t>
+          <t>2,53; 8,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,88</t>
+          <t>1,17; 6,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 8,65</t>
+          <t>-8,18; 8,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 111,92</t>
+          <t>25,92; 120,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 109,75</t>
+          <t>13,14; 104,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,33; 56,45</t>
+          <t>-41,42; 52,5</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,37; 17,71</t>
+          <t>9,94; 17,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 10,7</t>
+          <t>3,51; 10,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 17,85</t>
+          <t>4,12; 18,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114,54; 341,49</t>
+          <t>110,24; 344,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,73; 126,5</t>
+          <t>28,88; 128,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,34; 106,84</t>
+          <t>21,2; 116,97</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,25; 20,5</t>
+          <t>15,31; 20,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,47</t>
+          <t>9,85; 14,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,43; 28,19</t>
+          <t>20,42; 27,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>411,48; —</t>
+          <t>407,39; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>304,9; 1786,44</t>
+          <t>293,42; 1699,18</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,07</t>
+          <t>8,02; 11,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,73</t>
+          <t>4,77; 7,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 15,51</t>
+          <t>7,5; 15,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109,12; 184,44</t>
+          <t>107,34; 184,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,42; 126,54</t>
+          <t>63,47; 122,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,42; 151,05</t>
+          <t>67,27; 155,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DCD-Clase-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,14</t>
+          <t>11,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>129,76%</t>
+          <t>133,24%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 11,41</t>
+          <t>2,09; 10,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 5,84</t>
+          <t>-1,61; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,06</t>
+          <t>7,41; 15,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,47; 347,16</t>
+          <t>28,31; 330,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 144,96</t>
+          <t>-24,02; 154,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,82; 207,4</t>
+          <t>69,1; 218,63</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>13,63</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>119,11%</t>
+          <t>137,91%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 12,56</t>
+          <t>3,71; 12,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 10,14</t>
+          <t>1,66; 9,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 17,0</t>
+          <t>9,79; 18,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,3; 332,02</t>
+          <t>53,47; 340,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,87; 355,08</t>
+          <t>20,7; 339,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,59; 212,27</t>
+          <t>77,71; 237,29</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23,16</t>
+          <t>17,91</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>257,69%</t>
+          <t>127,03%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 9,68</t>
+          <t>0,44; 10,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,57</t>
+          <t>6,05; 20,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,13; 32,76</t>
+          <t>11,67; 24,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 136,26</t>
+          <t>-0,12; 140,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73,99; 336,77</t>
+          <t>74,9; 350,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>108,68; 844,01</t>
+          <t>72,76; 201,33</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,42</t>
+          <t>2,36; 8,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,85</t>
+          <t>1,46; 6,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 8,35</t>
+          <t>4,93; 11,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,92; 120,03</t>
+          <t>22,81; 116,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,14; 104,73</t>
+          <t>16,0; 103,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,42; 52,5</t>
+          <t>27,03; 80,14</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,51</t>
+          <t>17,73</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>108,82%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 17,61</t>
+          <t>10,2; 17,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,76</t>
+          <t>3,21; 10,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 18,86</t>
+          <t>13,46; 21,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110,24; 344,52</t>
+          <t>117,67; 331,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,88; 128,47</t>
+          <t>27,18; 130,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,2; 116,97</t>
+          <t>70,79; 154,75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,32</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>746,87%</t>
+          <t>751,22%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,31; 20,27</t>
+          <t>15,47; 20,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,74</t>
+          <t>9,87; 14,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,42; 27,9</t>
+          <t>20,02; 27,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>407,39; —</t>
+          <t>355,57; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>293,42; 1699,18</t>
+          <t>319,27; 1902,27</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,39</t>
+          <t>14,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>101,09%</t>
+          <t>108,85%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,26</t>
+          <t>8,11; 11,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,73</t>
+          <t>4,75; 7,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 15,38</t>
+          <t>12,4; 15,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107,34; 184,56</t>
+          <t>108,86; 186,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,47; 122,41</t>
+          <t>62,13; 123,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,27; 155,08</t>
+          <t>89,72; 131,47</t>
         </is>
       </c>
     </row>
